--- a/results/Supplementary_Table_5_OddsRatioTest_hits.xlsx
+++ b/results/Supplementary_Table_5_OddsRatioTest_hits.xlsx
@@ -8,14 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvin/orb-selection/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF0CB8E-85E1-514F-A751-5C561DA4D668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438C29D7-B675-E54A-9ACD-F81B36B7F3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="600" windowWidth="25880" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6440" yWindow="1780" windowWidth="25880" windowHeight="22840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$833</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="0">Sheet1!$K$1:$T$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -8026,7 +8043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J833"/>
+  <dimension ref="A1:T833"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -8040,7 +8057,7 @@
     <col min="10" max="10" width="78" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8071,8 +8088,18 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -8104,7 +8131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -8127,7 +8154,7 @@
         <v>4.3930242982408529</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -8159,7 +8186,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -8182,7 +8209,7 @@
         <v>2.825520337068077</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8214,7 +8241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -8246,7 +8273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -8269,7 +8296,7 @@
         <v>2.9226952011448208</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -8301,7 +8328,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -8333,7 +8360,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -8365,7 +8392,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -8397,7 +8424,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -8429,7 +8456,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -8461,7 +8488,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -8493,7 +8520,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>55</v>
       </c>
